--- a/clases/clase5/bbdd/poemas.xlsx
+++ b/clases/clase5/bbdd/poemas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matdknu/Dropbox/CIIR/cursoR-etnicidad/clases/clase5/bbdd/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1979302-0618-C54D-8F89-892B0C2A98DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10EABAFA-3EA3-0844-A11B-FD5B0E3013B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" xr2:uid="{BA92DB5D-77FA-ED46-9912-9FF36A855CE3}"/>
   </bookViews>
